--- a/assessed_genes_diseases.xlsx
+++ b/assessed_genes_diseases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marlenlauffer/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C186002-427E-6E45-A839-EE47316AB921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{8C47B0C5-D430-824C-A78B-32B51BC7CB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,6 +78,9 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>Eligibility</t>
+  </si>
+  <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/30643219/</t>
   </si>
   <si>
@@ -139,9 +142,6 @@
   </si>
   <si>
     <t>Therapeutic Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eligibility </t>
   </si>
   <si>
     <t>AP3B2</t>
@@ -627,58 +627,58 @@
         <v>2</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>13</v>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -791,10 +791,10 @@
         <v>53</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -802,7 +802,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>54</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -920,37 +920,37 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="6"/>
     </row>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19" s="6"/>
     </row>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I42" s="6"/>
     </row>
